--- a/VanHanhCD1/wwwroot/templates/BMVH_LUYENCOC_LBMT2.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_LUYENCOC_LBMT2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\LC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E13CC0-2A22-46DF-8AA1-0FC1B2F916CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D88E9AA-9D7E-42FE-9E6F-77D4E1CE1BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,18 +166,6 @@
     <t>SỔ THEO DÕI THÔNG SỐ VẬN HÀNH LỌC BỤI MÔI TRƯỜNG MẶT ĐẤT 2</t>
   </si>
   <si>
-    <t>TE_14601A</t>
-  </si>
-  <si>
-    <t>TE_14601B</t>
-  </si>
-  <si>
-    <t>TE_14602</t>
-  </si>
-  <si>
-    <t>PT_14602</t>
-  </si>
-  <si>
     <t>BY_S201AI01_7_I</t>
   </si>
   <si>
@@ -218,6 +206,18 @@
   </si>
   <si>
     <t>LB2_W</t>
+  </si>
+  <si>
+    <t>TE_14601</t>
+  </si>
+  <si>
+    <t>TE_14603</t>
+  </si>
+  <si>
+    <t>TE_14604</t>
+  </si>
+  <si>
+    <t>PT_14603</t>
   </si>
 </sst>
 </file>
@@ -576,6 +576,39 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -612,71 +645,38 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1656,76 +1656,76 @@
       </c>
     </row>
     <row r="3" spans="1:27" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
     </row>
     <row r="4" spans="1:27" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="23"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
     </row>
     <row r="5" spans="1:27" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="28" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="30"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="41"/>
     </row>
     <row r="6" spans="1:27" s="15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="38"/>
       <c r="C6" s="14">
         <v>0.33333333333333331</v>
       </c>
@@ -1800,10 +1800,10 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="19"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="17">
         <f>Sheet2!D6</f>
         <v>0</v>
@@ -1903,10 +1903,10 @@
       <c r="AA7" s="15"/>
     </row>
     <row r="8" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="19"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="17">
         <f>Sheet2!D7</f>
         <v>0</v>
@@ -2006,10 +2006,10 @@
       <c r="AA8" s="15"/>
     </row>
     <row r="9" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="19"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="17">
         <f>Sheet2!D8</f>
         <v>0</v>
@@ -2109,10 +2109,10 @@
       <c r="AA9" s="15"/>
     </row>
     <row r="10" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="19"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="17">
         <f>Sheet2!D9</f>
         <v>0</v>
@@ -2212,10 +2212,10 @@
       <c r="AA10" s="15"/>
     </row>
     <row r="11" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="19"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="17">
         <f>Sheet2!D10</f>
         <v>0</v>
@@ -2315,10 +2315,10 @@
       <c r="AA11" s="15"/>
     </row>
     <row r="12" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="17">
         <f>Sheet2!D11</f>
         <v>0</v>
@@ -2418,7 +2418,7 @@
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -2523,7 +2523,7 @@
       <c r="AA13" s="15"/>
     </row>
     <row r="14" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="14" t="s">
         <v>20</v>
       </c>
@@ -2626,10 +2626,10 @@
       <c r="AA14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="17">
         <f>Sheet2!D14</f>
         <v>0</v>
@@ -2729,10 +2729,10 @@
       <c r="AA15" s="15"/>
     </row>
     <row r="16" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="17">
         <f>Sheet2!D15</f>
         <v>0</v>
@@ -2832,10 +2832,10 @@
       <c r="AA16" s="15"/>
     </row>
     <row r="17" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="17">
         <f>Sheet2!D16</f>
         <v>0</v>
@@ -2935,10 +2935,10 @@
       <c r="AA17" s="15"/>
     </row>
     <row r="18" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="17">
         <f>Sheet2!D17</f>
         <v>0</v>
@@ -3038,10 +3038,10 @@
       <c r="AA18" s="15"/>
     </row>
     <row r="19" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="19"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="17">
         <f>Sheet2!D18</f>
         <v>0</v>
@@ -3141,10 +3141,10 @@
       <c r="AA19" s="15"/>
     </row>
     <row r="20" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="19"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="17">
         <f>Sheet2!D19</f>
         <v>0</v>
@@ -3244,10 +3244,10 @@
       <c r="AA20" s="15"/>
     </row>
     <row r="21" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="17">
         <f>Sheet2!D20</f>
         <v>0</v>
@@ -3347,10 +3347,10 @@
       <c r="AA21" s="15"/>
     </row>
     <row r="22" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="17">
         <f>Sheet2!D21</f>
         <v>0</v>
@@ -3450,10 +3450,10 @@
       <c r="AA22" s="15"/>
     </row>
     <row r="23" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="19"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="17">
         <f>Sheet2!D22</f>
         <v>0</v>
@@ -3553,10 +3553,10 @@
       <c r="AA23" s="15"/>
     </row>
     <row r="24" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="19"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="18">
         <f>Sheet2!D23</f>
         <v>0</v>
@@ -3656,104 +3656,104 @@
       <c r="AA24" s="15"/>
     </row>
     <row r="25" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="33" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="33" t="s">
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="W25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="35"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="22"/>
+      <c r="Z25" s="23"/>
       <c r="AA25" s="15"/>
     </row>
     <row r="26" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="36" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="36" t="s">
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
-      <c r="T26" s="37"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="37"/>
-      <c r="Z26" s="38"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="26"/>
       <c r="AA26" s="15"/>
     </row>
     <row r="27" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="31"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="39" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="39" t="s">
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="40"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="41"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="29"/>
       <c r="AA27" s="15"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
@@ -3764,23 +3764,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:N25"/>
-    <mergeCell ref="O25:Z25"/>
-    <mergeCell ref="C26:N26"/>
-    <mergeCell ref="O26:Z26"/>
-    <mergeCell ref="C27:N27"/>
-    <mergeCell ref="O27:Z27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A3:B3"/>
@@ -3793,6 +3776,23 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:N25"/>
+    <mergeCell ref="O25:Z25"/>
+    <mergeCell ref="C26:N26"/>
+    <mergeCell ref="O26:Z26"/>
+    <mergeCell ref="C27:N27"/>
+    <mergeCell ref="O27:Z27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="62" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -3811,12 +3811,13 @@
     <col min="4" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="19" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="51"/>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="A1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -3831,58 +3832,58 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
+      <c r="R1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="47" t="s">
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -3914,10 +3915,10 @@
       <c r="U4" s="3"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="50"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
@@ -4000,7 +4001,7 @@
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -4033,7 +4034,7 @@
       </c>
       <c r="B7" s="43"/>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -4066,7 +4067,7 @@
       </c>
       <c r="B8" s="43"/>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -4099,7 +4100,7 @@
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -4132,7 +4133,7 @@
       </c>
       <c r="B10" s="43"/>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -4165,7 +4166,7 @@
       </c>
       <c r="B11" s="43"/>
       <c r="C11" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -4193,14 +4194,14 @@
       <c r="AA11" s="6"/>
     </row>
     <row r="12" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="51" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4228,12 +4229,12 @@
       <c r="AA12" s="6"/>
     </row>
     <row r="13" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4266,7 +4267,7 @@
       </c>
       <c r="B14" s="43"/>
       <c r="C14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -4299,7 +4300,7 @@
       </c>
       <c r="B15" s="43"/>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -4332,7 +4333,7 @@
       </c>
       <c r="B16" s="43"/>
       <c r="C16" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -4365,7 +4366,7 @@
       </c>
       <c r="B17" s="43"/>
       <c r="C17" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -4393,12 +4394,12 @@
       <c r="AA17" s="6"/>
     </row>
     <row r="18" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="52"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -4431,7 +4432,7 @@
       </c>
       <c r="B19" s="43"/>
       <c r="C19" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -4464,7 +4465,7 @@
       </c>
       <c r="B20" s="43"/>
       <c r="C20" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -4497,7 +4498,7 @@
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -4530,7 +4531,7 @@
       </c>
       <c r="B22" s="43"/>
       <c r="C22" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -4563,7 +4564,7 @@
       </c>
       <c r="B23" s="43"/>
       <c r="C23" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -4592,6 +4593,19 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E2:Q3"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:C3"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A19:B19"/>
@@ -4601,19 +4615,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E2:Q3"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
